--- a/outputs/tower_example.xlsx
+++ b/outputs/tower_example.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_Px</t>
+          <t>env1.distLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 153.71553661127714, 168.2591010840852, 152.9239219923508, 171.59711922381467, 186.57677505331458, 198.8878313199889]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_Py</t>
+          <t>env1.distLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_Pz</t>
+          <t>env1.distLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_qdyn</t>
+          <t>env1.distLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_z</t>
+          <t>env1.distLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>env1.distLoads.waveLoads_beta</t>
+          <t>env1.distLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -586,17 +586,15 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>yaw</t>
+          <t>env1.distLoads.waveLoads_Px</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -606,12 +604,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -619,7 +617,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>env1.Uref</t>
+          <t>env1.distLoads.waveLoads_Py</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,12 +627,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[11.73732]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -642,7 +640,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wind_reference_height</t>
+          <t>env1.distLoads.waveLoads_Pz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -652,12 +650,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -665,7 +663,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>z0</t>
+          <t>env1.distLoads.waveLoads_qdyn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -675,12 +673,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -688,7 +686,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shearExp</t>
+          <t>env1.distLoads.waveLoads_z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -696,10 +694,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[0.2]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -707,7 +709,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beta_wind</t>
+          <t>env1.distLoads.waveLoads_beta</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -720,32 +722,30 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rho_air</t>
+          <t>z_global</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[1.225]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mu_air</t>
+          <t>yaw</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,20 +763,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kg/m/s</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>[1.7934e-05]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cd_usr</t>
+          <t>env1.Uref</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -784,18 +782,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[-1. -1. -1. -1. -1. -1. -1.]</t>
-        </is>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.73732</v>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_Px</t>
+          <t>wind_reference_height</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -805,20 +805,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>90</v>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_Py</t>
+          <t>z0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -828,20 +826,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_Pz</t>
+          <t>shearExp</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -849,22 +845,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.2</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_qdyn</t>
+          <t>env1.windLoads.U</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -874,12 +864,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 8.158137379714614, 9.371238987917998, 10.16284414354436, 10.764726809705484, 11.256024125067727, 11.674042349780658]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -887,12 +877,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_z</t>
+          <t>outer_diameter_full</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -902,7 +892,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[6.9444087559667524, 5.981092122436499, 5.017775488906244, 4.05445885537599, 3.99297257025066, 3.93148628512533, 3.87]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -910,7 +900,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>env2.distLoads.waveLoads_beta</t>
+          <t>beta_wind</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -923,17 +913,15 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D22" t="n">
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>env2.Uref</t>
+          <t>rho_air</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -943,20 +931,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[70.]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.225</v>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>s_all</t>
+          <t>mu_air</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -964,18 +950,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>kg/m/s</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.7934e-05</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tower_height</t>
+          <t>cd_usr</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -983,14 +971,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[87.6]</t>
+          <t>[-1.0, -1.0, -1.0, -1.0, -1.0, -1.0, -1.0]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -998,7 +982,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rna_mass</t>
+          <t>env2.distLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1008,12 +992,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[285598.8]</t>
+          <t>[0.0, 7016.411037436151, 7632.243738260155, 6882.244327637181, 7719.9797788202995, 8405.334019197559, 8975.908423016774]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1021,7 +1005,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rna_I</t>
+          <t>env2.distLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1031,13 +1015,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[1.14930678e+08 2.20354030e+07 1.87597425e+07 0.00000000e+00
- 5.03710467e+05 0.00000000e+00]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1045,7 +1028,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rna_cg</t>
+          <t>env2.distLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1055,12 +1038,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[-1.13197635  0.          0.50875268]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1068,7 +1051,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tower.rna_F</t>
+          <t>env2.distLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1078,14 +1061,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[[ 1284744.19620519   930198.60063279]
- [       0.                0.        ]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1093,7 +1074,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tower.rna_M</t>
+          <t>env2.distLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1103,14 +1084,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[[ 3963732.76208099 -1683669.22411597]
- [-2275104.79420872 -2522475.34625363]
- [ -346781.68192839   147301.97023764]]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1118,7 +1097,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>member.ca_usr_grid</t>
+          <t>env2.distLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1126,18 +1105,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[0. 0. 0.]</t>
-        </is>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>member.cd_usr_grid</t>
+          <t>env2.distLoads.waveLoads_Px</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1145,10 +1126,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1156,7 +1141,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rho_water</t>
+          <t>env2.distLoads.waveLoads_Py</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1166,12 +1151,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1179,7 +1164,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>member.s_ghost1</t>
+          <t>env2.distLoads.waveLoads_Pz</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1187,10 +1172,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1198,7 +1187,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>member.s_ghost2</t>
+          <t>env2.distLoads.waveLoads_qdyn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1206,10 +1195,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N/m**2</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[1.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1217,7 +1210,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tower_s</t>
+          <t>env2.distLoads.waveLoads_z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1225,10 +1218,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[0.  0.5 1. ]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1236,7 +1233,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>member.s_const1</t>
+          <t>env2.distLoads.waveLoads_beta</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1244,18 +1241,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>member.s_const2</t>
+          <t>env2.Uref</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1263,18 +1262,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>70</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tower_layer_thickness</t>
+          <t>env2.windLoads.U</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1284,12 +1285,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[[0.03061479 0.00450829 0.02405431]]</t>
+          <t>[0.0, 48.65417459692868, 55.8889703232305, 60.610010636849395, 64.19956827277299, 67.12960784529525, 69.6226195149017]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1297,12 +1298,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tower_outer_diameter_in</t>
+          <t>joint1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1312,7 +1313,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[6.78243547 4.16538692 3.87      ]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1320,22 +1321,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E_mat</t>
+          <t>joint2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[[2.1e+11 2.1e+11 2.1e+11]]</t>
+          <t>[0.0, 0.0, 87.6]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1343,22 +1344,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E_user</t>
+          <t>s_full</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.16666666666666666, 0.3333333333333333, 0.5, 0.6666666666666666, 0.8333333333333333, 1.0]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1366,7 +1367,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>G_mat</t>
+          <t>s_all</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1374,14 +1375,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[[8.08e+10 8.08e+10 8.08e+10]]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1389,7 +1386,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sigma_y_mat</t>
+          <t>g2e1.Px_global</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1399,12 +1396,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[4.5e+08]</t>
+          <t>[0.0, 153.71553661127714, 168.2591010840852, 152.9239219923508, 171.59711922381467, 186.57677505331458, 198.8878313199889]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1412,7 +1409,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sigma_ult_mat</t>
+          <t>g2e1.Py_global</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1422,12 +1419,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[[6.e+08 6.e+08 6.e+08]]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1435,7 +1432,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wohler_exp_mat</t>
+          <t>g2e1.Pz_global</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1443,10 +1440,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[10.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1454,7 +1455,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>wohler_A_mat</t>
+          <t>g2e1.qdyn_global</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1462,10 +1463,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[10.]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1473,7 +1478,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rho_mat</t>
+          <t>g2e2.Px_global</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1483,12 +1488,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[8500.]</t>
+          <t>[0.0, 7016.411037436151, 7632.243738260155, 6882.244327637181, 7719.9797788202995, 8405.334019197559, 8975.908423016774]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1496,7 +1501,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>unit_cost_mat</t>
+          <t>g2e2.Py_global</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1506,12 +1511,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[2.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1519,7 +1524,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outfitting_factor_in</t>
+          <t>g2e2.Pz_global</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1527,10 +1532,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[1.07]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1538,7 +1547,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tower_layer_materials</t>
+          <t>g2e2.qdyn_global</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1548,12 +1557,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1561,7 +1570,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>member.ballast_materials</t>
+          <t>lc1:Px</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1571,12 +1580,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1584,7 +1593,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>material_names</t>
+          <t>lc1:Py</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1594,12 +1603,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1607,7 +1616,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>labor_cost_rate</t>
+          <t>lc1:Pz</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1617,12 +1626,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USD/min</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[1.66666667]</t>
+          <t>[0.0, -153.71553661127714, -168.2591010840852, -152.9239219923508, -171.59711922381467, -186.57677505331458, -198.8878313199889]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1630,7 +1639,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>painting_cost_rate</t>
+          <t>lc1:qdyn</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1640,12 +1649,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USD/m**2</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[30.]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1653,7 +1662,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hub_height</t>
+          <t>lc2:Px</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1663,12 +1672,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[87.6]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1676,7 +1685,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>foundation_height</t>
+          <t>lc2:Py</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1686,12 +1695,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1699,12 +1708,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_Px</t>
+          <t>lc2:Pz</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1714,8 +1723,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[  0.         151.3415607  169.13352946 158.68050269 175.88853604
- 188.91149088 198.88783132]</t>
+          <t>[0.0, -7016.411037436151, -7632.243738260155, -6882.244327637181, -7719.9797788202995, -8405.334019197559, -8975.908423016774]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -1723,22 +1731,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_Py</t>
+          <t>lc2:qdyn</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -1746,22 +1754,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_Pz</t>
+          <t>z_full</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -1769,23 +1777,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_qdyn</t>
+          <t>t_full</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[0.019498302810239246, 0.019498302810239246, 0.019498302810239246, 0.016950804478426052, 0.016950804478426052, 0.016950804478426052]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -1793,12 +1800,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_z</t>
+          <t>tower_height</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1806,32 +1813,30 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
-        </is>
+      <c r="D62" t="n">
+        <v>87.59999999999999</v>
       </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>env1.distLoads.windLoads_beta</t>
+          <t>E_full</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1839,7 +1844,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>z_global</t>
+          <t>G_full</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1849,12 +1854,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
+          <t>[80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1862,23 +1867,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>env1.windLoads.U</t>
+          <t>rho_full</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[ 0.          8.15813738  9.37123899 10.16284414 10.76472681 11.25602413
- 11.67404235]</t>
+          <t>[8500.0, 8500.0, 8500.0, 8500.0, 8500.0, 8500.0]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1886,7 +1890,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outer_diameter_full</t>
+          <t>sigma_y_full</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1896,13 +1900,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[6.78243547 5.91008595 5.03773644 4.16538692 4.06692462 3.96846231
- 3.87      ]</t>
+          <t>[450000000.0, 450000000.0, 450000000.0, 450000000.0, 450000000.0, 450000000.0]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -1910,23 +1913,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_Px</t>
+          <t>section_A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[   0.         6893.09009634 7676.56806418 7137.64623057 7918.54479894
- 8516.69916741 8975.90842302]</t>
+          <t>[0.3946860801098097, 0.3356774214473268, 0.27666876278484387, 0.21337033972293384, 0.2100960399210665, 0.20682174011919782]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -1934,22 +1936,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_Py</t>
+          <t>section_Asx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.23997118964800285, 0.20414216299805857, 0.16831340385630117, 0.12980030804908094, 0.12781223432357872, 0.12582416244685188]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -1957,22 +1959,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_Pz</t>
+          <t>section_Asy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.23997118964800285, 0.20414216299805857, 0.16831340385630117, 0.12980030804908094, 0.12781223432357872, 0.12582416244685188]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -1980,23 +1982,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_qdyn</t>
+          <t>section_Ixx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[2.048217407429407, 1.2600521963741707, 0.7055131677241467, 0.4281929942764957, 0.4087815208467369, 0.38996575844393944]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2004,22 +2005,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_z</t>
+          <t>section_Iyy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
+          <t>[2.048217407429407, 1.2600521963741707, 0.7055131677241467, 0.4281929942764957, 0.4087815208467369, 0.38996575844393944]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2027,22 +2028,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>env2.distLoads.windLoads_beta</t>
+          <t>section_J0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[4.096434814858814, 2.5201043927483413, 1.4110263354482935, 0.8563859885529914, 0.8175630416934738, 0.7799315168878789]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2050,23 +2051,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>env2.windLoads.U</t>
+          <t>section_rho</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[ 0.         48.6541746  55.88897032 60.61001064 64.19956827 67.12960785
- 69.62261951]</t>
+          <t>[9095.0, 9095.0, 9095.0, 9095.0, 9095.0, 9095.0]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2074,7 +2074,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>joint1</t>
+          <t>section_E</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0, 210000000000.0]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2097,7 +2097,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>joint2</t>
+          <t>section_G</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[ 0.   0.  87.6]</t>
+          <t>[80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0, 80800000000.0]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>s_full</t>
+          <t>section_L</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2135,8 +2135,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[0.         0.16666667 0.33333333 0.5        0.66666667 0.83333333
- 1.        ]</t>
+          <t>[14.599999999999998, 14.599999999999998, 14.600000000000001, 14.599999999999994, 14.599999999999994, 14.600000000000009]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2144,23 +2143,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>g2e1.Px_global</t>
+          <t>post.cylinder_Fz</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[  0.         151.3415607  169.13352946 158.68050269 175.88853604
- 188.91149088 198.88783132]</t>
+          <t>[[-4544592.622056397, -5059650.423935822], [-4105162.3238747856, -4516681.208264228], [-3742576.0671883076, -4051519.9310538517], [-3462389.8984045135, -3668148.7953211386], [-3186224.1643253956, -3278033.9326571384], [-2914124.844005121, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2168,22 +2166,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>g2e1.Py_global</t>
+          <t>post.cylinder_Vx</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[1285238.4043869115, 930576.6322370842], [1286097.8934733793, 931397.019623898], [1286916.2528408542, 932204.6731474921], [1287453.2592315823, 932837.2813826948], [1288280.5799453706, 933744.9353920519], [1288647.8186224997, 934202.6490297467]]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2191,22 +2189,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>g2e1.Pz_global</t>
+          <t>post.cylinder_Vy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[-18.765764536336064, 8.53598613559734], [-58.02487879083492, 30.58131721999962], [-107.4146036352031, 59.15196234197356], [-160.36497919354588, 93.35996334557422], [-253.8755525201559, 152.6752626481466], [-346.8634190177545, 214.37659653648734]]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2214,23 +2212,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>g2e1.qdyn_global</t>
+          <t>post.cylinder_Mxx</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[[4290877.763432895, -1831495.2536678775], [4273372.652325834, -1823180.615096555], [4237898.836773356, -1806529.7130356994], [4175375.814008143, -1777668.6551501239], [4082441.520206839, -1735707.0848135897], [3963851.324185379, -1683742.331208717]]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2238,23 +2235,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>g2e2.Px_global</t>
+          <t>post.cylinder_Myy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[   0.         6893.09009634 7676.56806418 7137.64623057 7918.54479894
- 8516.69916741 8975.90842302]</t>
+          <t>[[96317618.26315734, 69030462.77466904], [77152307.69559985, 55123988.63890882], [57678444.10838093, 40978912.747313626], [37866284.06151751, 26583206.922303095], [17815762.835481524, 12028457.115821362], [-2274916.13560766, -2522314.562396005]]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2262,22 +2258,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>g2e2.Py_global</t>
+          <t>post.cylinder_Mzz</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[-346836.7097078701, 147327.95330848012], [-346839.7972184067, 147329.45402743277], [-346845.3753805976, 147331.7378701903], [-346856.97858079086, 147336.59471315128], [-346852.4262340079, 147333.80635760282], [-346847.8133335625, 147330.8703587166]]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2285,22 +2281,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>g2e2.Pz_global</t>
+          <t>qdyn</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[0.0, 0.0], [40.765063372606804, 1449.9275822464074], [53.789823603313046, 1913.1909148219506], [63.261083165159015, 2250.063701006886], [70.97609776365012, 2524.4705469263954], [77.60257345126534, 2760.160352796165], [83.47349968048928, 2968.9768532215226]]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2308,23 +2304,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>g2e2.qdyn_global</t>
+          <t>nodes_xyz</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 14.599999999999998], [0.0, 0.0, 29.199999999999996], [0.0, 0.0, 43.8], [0.0, 0.0, 58.39999999999999], [0.0, 0.0, 72.99999999999999], [0.0, 0.0, 87.6]]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2332,45 +2327,43 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lc1:Px</t>
+          <t>rna_mass</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>285598.8</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lc1:Py</t>
+          <t>rna_I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[114930678.0, 22035403.0, 18759742.5, 0.0, 503710.467, 0.0]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2378,23 +2371,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lc1:Pz</t>
+          <t>rna_cg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[   0.         -151.3415607  -169.13352946 -158.68050269 -175.88853604
- -188.91149088 -198.88783132]</t>
+          <t>[-1.13197635, 0.0, 0.50875268]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2402,23 +2394,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lc1:qdyn</t>
+          <t>tower.rna_F</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[[1284744.19620519, 930198.60063279], [0.0, 0.0], [-2914124.84400512, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2426,22 +2417,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lc2:Px</t>
+          <t>tower.rna_M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[3963732.76208099, -1683669.22411597], [-2275104.79420872, -2522475.34625363], [-346781.68192839, 147301.97023764]]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2449,12 +2440,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lc2:Py</t>
+          <t>Px</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2464,7 +2455,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2472,12 +2463,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lc2:Pz</t>
+          <t>Py</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2487,8 +2478,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[    0.         -6893.09009634 -7676.56806418 -7137.64623057
- -7918.54479894 -8516.69916741 -8975.90842302]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2496,23 +2486,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>lc2:qdyn</t>
+          <t>Pz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[[0.0, 0.0], [-153.71553661127714, -7016.411037436151], [-168.2591010840852, -7632.243738260155], [-152.9239219923508, -6882.244327637181], [-171.59711922381467, -7719.9797788202995], [-186.57677505331458, -8405.334019197559], [-198.8878313199889, -8975.908423016774]]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2520,7 +2509,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>z_full</t>
+          <t>tower_mass</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2530,20 +2519,18 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>217414.8618441729</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>t_full</t>
+          <t>tower_center_of_mass</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2556,17 +2543,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>[0.01756154 0.01756154 0.01756154 0.0142813  0.0142813  0.0142813 ]</t>
-        </is>
+      <c r="D94" t="n">
+        <v>37.51125403935141</v>
       </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>E_full</t>
+          <t>tower_I_base</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2576,12 +2561,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[2.1e+11 2.1e+11 2.1e+11 2.1e+11 2.1e+11 2.1e+11]</t>
+          <t>[447711732.9598199, 447711732.9598199, 1399575.1876188335, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -2589,22 +2574,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>G_full</t>
+          <t>member.gc.d</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[8.08e+10 8.08e+10 8.08e+10 8.08e+10 8.08e+10 8.08e+10]</t>
+          <t>[6.9444087559667524, 4.05445885537599, 3.87]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2612,22 +2597,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rho_full</t>
+          <t>member.gc.t</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[8500. 8500. 8500. 8500. 8500. 8500.]</t>
+          <t>[0.019498302810239246, 0.016950804478426052]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2635,7 +2620,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sigma_y_full</t>
+          <t>member.s</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2643,14 +2628,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[4.5e+08 4.5e+08 4.5e+08 4.5e+08 4.5e+08 4.5e+08]</t>
+          <t>[0.0, 0.5, 1.0]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2658,7 +2639,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>section_A</t>
+          <t>member.height</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2668,20 +2649,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[0.37360337 0.32210579 0.2706082  0.19691726 0.19219041 0.18746357]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>87.59999999999999</v>
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>section_Asx</t>
+          <t>tower_outer_diameter</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2691,12 +2670,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[0.21226855 0.18304563 0.15382287 0.11191691 0.10923462 0.10655233]</t>
+          <t>[6.9444087559667524, 4.05445885537599, 3.87]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -2704,22 +2683,18 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>section_Asy</t>
+          <t>member.ca_usr_grid</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>m**2</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[0.21226855 0.18304563 0.15382287 0.11191691 0.10923462 0.10655233]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2727,22 +2702,18 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>section_Ixx</t>
+          <t>member.cd_usr_grid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[1.87047991 1.1987191  0.71079864 0.41415584 0.38504179 0.35732518]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2750,7 +2721,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>section_Iyy</t>
+          <t>tower_wall_thickness</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2760,12 +2731,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[1.87047991 1.1987191  0.71079864 0.41415584 0.38504179 0.35732518]</t>
+          <t>[0.019498302810239246, 0.016950804478426052]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -2773,7 +2744,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>section_J0</t>
+          <t>member.E</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2783,12 +2754,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[3.74095982 2.3974382  1.42159728 0.82831168 0.77008358 0.71465036]</t>
+          <t>[210000000000.0, 210000000000.0]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -2796,7 +2767,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>section_rho</t>
+          <t>member.G</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2806,12 +2777,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[8500. 8500. 8500. 8500. 8500. 8500.]</t>
+          <t>[80800000000.0, 80800000000.0]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -2819,7 +2790,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>section_E</t>
+          <t>member.sigma_y</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2834,7 +2805,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[2.1e+11 2.1e+11 2.1e+11 2.1e+11 2.1e+11 2.1e+11]</t>
+          <t>[450000000.0, 450000000.0]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -2842,7 +2813,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>section_G</t>
+          <t>member.rho</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2852,12 +2823,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[8.08e+10 8.08e+10 8.08e+10 8.08e+10 8.08e+10 8.08e+10]</t>
+          <t>[8500.0, 8500.0]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -2865,7 +2836,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>section_L</t>
+          <t>member.unit_cost</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2875,12 +2846,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[14.6 14.6 14.6 14.6 14.6 14.6]</t>
+          <t>[2.0, 2.0]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -2888,27 +2859,18 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>post.cylinder_Fz</t>
+          <t>member.outfitting_factor</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[[-4349646.81775228 -4872450.88627529]
- [-3955339.11065362 -4375164.32950331]
- [-3623649.11824756 -3938781.12201792]
- [-3381589.68356992 -3590328.5189508 ]
- [-3145064.16518961 -3237661.89709768]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[1.07, 1.07]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -2916,111 +2878,73 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>post.cylinder_Vx</t>
+          <t>rho_water</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>[[1285223.92883864  930568.12549209]
- [1286054.13431463  931381.50956449]
- [1286827.30616763  932170.86795165]
- [1287171.46669971  932687.2888348 ]
- [1287893.29133193  933534.35080664]
- [1288201.35371041  933952.44178088]]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
       </c>
       <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>post.cylinder_Vy</t>
+          <t>member.s_ghost1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>[[ -18.2090241     8.34144263]
- [ -56.07168431   30.14563474]
- [-102.44697284   57.83271087]
- [-142.90930477   87.57210187]
- [-225.75952273  143.40405172]
- [-308.91537417  202.12683454]]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>0</v>
       </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>post.cylinder_Mxx</t>
+          <t>member.s_ghost2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>[[ 4297041.58485836 -1834651.88849187]
- [ 4278995.50136644 -1826025.02311278]
- [ 4243354.70033699 -1809201.36194055]
- [ 4180906.90705807 -1780251.68693602]
- [ 4086669.56457052 -1737601.6932439 ]
- [ 3963842.64578302 -1683740.94855524]]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>post.cylinder_Myy</t>
+          <t>tower_s</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>N*m</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[[96402464.36660439 69106267.72841041]
- [77223950.80432796 55187110.18180166]
- [57742653.41236804 41032950.91426268]
- [37926035.15853652 26630228.20721585]
- [17855596.37986553 12058094.60763581]
- [-2274928.61633226 -2522316.0967429 ]]</t>
+          <t>[0.0, 0.5, 1.0]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3028,69 +2952,46 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>post.cylinder_Mzz</t>
+          <t>member.s_const1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>[[-346836.89386053  147328.21230941]
- [-346839.64786186  147329.55234485]
- [-346844.42504904  147331.45091846]
- [-346860.67810759  147338.44418837]
- [-346857.21350947  147336.03458721]
- [-346853.70101696  147333.46255849]]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0</v>
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>qdyn</t>
+          <t>member.s_const2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>[[   0.            0.        ]
- [  40.76506337 1449.92758225]
- [  53.7898236  1913.19091482]
- [  63.26108317 2250.06370101]
- [  70.97609776 2524.47054693]
- [  77.60257345 2760.1603528 ]
- [  83.47349968 2968.97685322]]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>0</v>
       </c>
       <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nodes_xyz</t>
+          <t>tower_layer_thickness</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3100,13 +3001,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[[ 0.   0.   0. ]
- [ 0.   0.  14.6]
- [ 0.   0.  29.2]
- [ 0.   0.  43.8]
- [ 0.   0.  58.4]
- [ 0.   0.  73. ]
- [ 0.   0.  87.6]]</t>
+          <t>[[0.03495400690407969, 0.004042598716398804, 0.029859010240453298]]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3114,28 +3009,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Px</t>
+          <t>tower_outer_diameter_in</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[[0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]]</t>
+          <t>[6.9444087559667524, 4.05445885537599, 3.87]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3143,28 +3032,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Py</t>
+          <t>E_mat</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[[0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]]</t>
+          <t>[[210000000000.0, 210000000000.0, 210000000000.0]]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3172,51 +3055,43 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pz</t>
+          <t>E_user</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>[[    0.             0.        ]
- [ -151.3415607  -6893.09009634]
- [ -169.13352946 -7676.56806418]
- [ -158.68050269 -7137.64623057]
- [ -175.88853604 -7918.54479894]
- [ -188.91149088 -8516.69916741]
- [ -198.88783132 -8975.90842302]]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
       </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tower_mass</t>
+          <t>G_mat</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[191472.47476739]</t>
+          <t>[[80800000000.0, 80800000000.0, 80800000000.0]]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3224,46 +3099,43 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tower_center_of_mass</t>
+          <t>sigma_y_mat</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>[37.07079565]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>450000000</v>
       </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tower_I_base</t>
+          <t>sigma_ult_mat</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[3.85873865e+08 3.85873865e+08 1.23099138e+06 0.00000000e+00
- 0.00000000e+00 0.00000000e+00]</t>
+          <t>[[600000000.0, 600000000.0, 600000000.0]]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3271,156 +3143,134 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>member.gc.d</t>
+          <t>wohler_exp_mat</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>[6.78243547 4.16538692 3.87      ]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>10</v>
       </c>
       <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>member.gc.t</t>
+          <t>wohler_A_mat</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>[0.01756154 0.0142813 ]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>10</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>member.s</t>
+          <t>rho_mat</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>[0.  0.5 1. ]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>8500</v>
       </c>
       <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>member.height</t>
+          <t>unit_cost_mat</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>[87.6]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>tower_outer_diameter</t>
+          <t>outfitting_factor_in</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>[6.78243547 4.16538692 3.87      ]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>1.07</v>
       </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>tower_wall_thickness</t>
+          <t>tower_layer_materials</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>[0.01756154 0.0142813 ]</t>
-        </is>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>member.E</t>
+          <t>member.ballast_materials</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[2.1e+11 2.1e+11]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -3428,30 +3278,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>member.G</t>
+          <t>material_names</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>[8.08e+10 8.08e+10]</t>
-        </is>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>member.sigma_y</t>
+          <t>outfitting_full</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3459,14 +3305,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[4.5e+08 4.5e+08]</t>
+          <t>[1.07, 1.07, 1.07, 1.07, 1.07, 1.07]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -3474,7 +3316,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>member.rho</t>
+          <t>member.unit_cost_full</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3484,12 +3326,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[8500. 8500.]</t>
+          <t>[2.0, 2.0, 2.0, 2.0, 2.0, 2.0]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -3497,115 +3339,112 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>member.unit_cost</t>
+          <t>labor_cost_rate</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>[2. 2.]</t>
-        </is>
+          <t>USD/min</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1.666666666666667</v>
       </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>member.outfitting_factor</t>
+          <t>painting_cost_rate</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>[1.07 1.07]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USD/m**2</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>30</v>
       </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>outfitting_full</t>
+          <t>tower_mass_user</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>[1.07 1.07 1.07 1.07 1.07 1.07]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>member.unit_cost_full</t>
+          <t>hub_height</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>[2. 2. 2. 2. 2. 2.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>87.59999999999999</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>env1.Px</t>
+          <t>foundation_height</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>[  0.         151.3415607  169.13352946 158.68050269 175.88853604
- 188.91149088 198.88783132]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>env1.Py</t>
+          <t>env1.Px</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3620,7 +3459,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 153.71553661127714, 168.2591010840852, 152.9239219923508, 171.59711922381467, 186.57677505331458, 198.8878313199889]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3628,7 +3467,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>env1.Pz</t>
+          <t>env1.Py</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3643,7 +3482,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -3651,7 +3490,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>env1.qdyn</t>
+          <t>env1.Pz</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3661,13 +3500,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -3675,7 +3513,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>env1.wind.U</t>
+          <t>env1.qdyn</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3685,13 +3523,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[ 0.          8.15813738  9.37123899 10.16284414 10.76472681 11.25602413
- 11.67404235]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -3699,7 +3536,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_Px</t>
+          <t>env1.wind.U</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3709,13 +3546,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[  0.         151.3415607  169.13352946 158.68050269 175.88853604
- 188.91149088 198.88783132]</t>
+          <t>[0.0, 8.158137379714614, 9.371238987917998, 10.16284414354436, 10.764726809705484, 11.256024125067727, 11.674042349780658]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -3723,7 +3559,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_Py</t>
+          <t>env1.windLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3738,7 +3574,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 153.71553661127714, 168.2591010840852, 152.9239219923508, 171.59711922381467, 186.57677505331458, 198.8878313199889]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -3746,7 +3582,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_Pz</t>
+          <t>env1.windLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3761,7 +3597,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -3769,7 +3605,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_qdyn</t>
+          <t>env1.windLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3779,13 +3615,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -3793,7 +3628,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_z</t>
+          <t>env1.windLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3803,12 +3638,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -3816,7 +3651,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>env1.windLoads.windLoads_beta</t>
+          <t>env1.windLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3826,12 +3661,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -3839,7 +3674,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>env2.Px</t>
+          <t>env1.windLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3849,21 +3684,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>[   0.         6893.09009634 7676.56806418 7137.64623057 7918.54479894
- 8516.69916741 8975.90842302]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>env2.Py</t>
+          <t>env2.Px</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3878,7 +3710,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 7016.411037436151, 7632.243738260155, 6882.244327637181, 7719.9797788202995, 8405.334019197559, 8975.908423016774]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -3886,7 +3718,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>env2.Pz</t>
+          <t>env2.Py</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3901,7 +3733,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -3909,7 +3741,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>env2.qdyn</t>
+          <t>env2.Pz</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3919,13 +3751,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -3933,7 +3764,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>env2.wind.U</t>
+          <t>env2.qdyn</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3943,13 +3774,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[ 0.         48.6541746  55.88897032 60.61001064 64.19956827 67.12960785
- 69.62261951]</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -3957,7 +3787,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_Px</t>
+          <t>env2.wind.U</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3967,13 +3797,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[   0.         6893.09009634 7676.56806418 7137.64623057 7918.54479894
- 8516.69916741 8975.90842302]</t>
+          <t>[0.0, 48.65417459692868, 55.8889703232305, 60.610010636849395, 64.19956827277299, 67.12960784529525, 69.6226195149017]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -3981,7 +3810,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_Py</t>
+          <t>env2.windLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3996,7 +3825,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 7016.411037436151, 7632.243738260155, 6882.244327637181, 7719.9797788202995, 8405.334019197559, 8975.908423016774]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4004,7 +3833,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_Pz</t>
+          <t>env2.windLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4019,7 +3848,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4027,7 +3856,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_qdyn</t>
+          <t>env2.windLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4037,13 +3866,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4051,7 +3879,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_z</t>
+          <t>env2.windLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4061,12 +3889,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4074,7 +3902,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>env2.windLoads.windLoads_beta</t>
+          <t>env2.windLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,12 +3912,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4097,7 +3925,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>g2e1.Px</t>
+          <t>env2.windLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4107,20 +3935,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>g2e1.Py</t>
+          <t>g2e1.Px</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4135,7 +3961,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -4143,7 +3969,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>g2e1.Pz</t>
+          <t>g2e1.Py</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4158,8 +3984,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[   0.         -151.3415607  -169.13352946 -158.68050269 -175.88853604
- -188.91149088 -198.88783132]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4167,7 +3992,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>g2e1.qdyn</t>
+          <t>g2e1.Pz</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4177,13 +4002,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[ 0.         40.76506337 53.7898236  63.26108317 70.97609776 77.60257345
- 83.47349968]</t>
+          <t>[0.0, -153.71553661127714, -168.2591010840852, -152.9239219923508, -171.59711922381467, -186.57677505331458, -198.8878313199889]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4191,7 +4015,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>g2e2.Px</t>
+          <t>g2e1.qdyn</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4201,12 +4025,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 40.765063372606804, 53.789823603313046, 63.261083165159015, 70.97609776365012, 77.60257345126534, 83.47349968048928]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4214,7 +4038,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>g2e2.Py</t>
+          <t>g2e2.Px</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4229,7 +4053,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -4237,7 +4061,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>g2e2.Pz</t>
+          <t>g2e2.Py</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4252,8 +4076,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[    0.         -6893.09009634 -7676.56806418 -7137.64623057
- -7918.54479894 -8516.69916741 -8975.90842302]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -4261,7 +4084,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>g2e2.qdyn</t>
+          <t>g2e2.Pz</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4271,13 +4094,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[   0.         1449.92758225 1913.19091482 2250.06370101 2524.47054693
- 2760.1603528  2968.97685322]</t>
+          <t>[0.0, -7016.411037436151, -7632.243738260155, -6882.244327637181, -7719.9797788202995, -8405.334019197559, -8975.908423016774]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -4285,7 +4107,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>post.axial_stress</t>
+          <t>g2e2.qdyn</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4300,12 +4122,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[[1.52059591e+08 1.04233187e+08]
- [1.64311153e+08 1.12491011e+08]
- [1.74020176e+08 1.18393120e+08]
- [1.72436136e+08 1.14397145e+08]
- [7.92009822e+07 4.67134065e+07]
- [9.51889604e+06 1.25196099e+06]]</t>
+          <t>[0.0, 1449.9275822464074, 1913.1909148219506, 2250.063701006886, 2524.4705469263954, 2760.160352796165, 2968.9768532215226]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -4313,7 +4130,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>post.shear_stress</t>
+          <t>post.axial_stress</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4328,12 +4145,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[[ 6348898.81083365  4508884.69526929]
- [ 7421824.46828741  5256441.71602957]
- [ 8926993.42813641  6298476.23837749]
- [12362967.78216862  8699834.52821724]
- [12694971.66335526  8930482.11626911]
- [13040941.26122593  9169197.08239274]]</t>
+          <t>[[163620889.18229672, 121763833.06053333], [180851215.09923542, 133814122.023406], [199449716.70051435, 146509434.49744448], [195219591.77149382, 142371190.0001329], [103745551.78700703, 74500938.15735635], [36947738.84337076, 29107601.20120912]]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -4341,7 +4153,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>post.hoop_stress</t>
+          <t>post.shear_stress</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4356,12 +4168,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[[  -3672.65301448 -130628.54476727]
- [  -7344.52135212 -261229.18022953]
- [  -7638.30031384 -271678.28013133]
- [  -9638.89910028 -342835.3720498 ]
- [ -10412.59602939 -370354.14486677]
- [ -11010.79659963 -391630.8812374 ]]</t>
+          <t>[[5629396.839358316, 3994084.2994830906], [6678452.278623977, 4723245.149009359], [8203465.37527358, 5775323.684374759], [10733573.707531337, 7532840.183117431], [10919969.089096237, 7662617.679900278], [11109017.527972022, 7793098.034613395]]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -4369,7 +4176,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>post.hoop_stress_euro</t>
+          <t>post.hoop_stress</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4384,12 +4191,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[[  -2387.22445941  -84908.55409872]
- [  -4773.93887888 -169798.9671492 ]
- [  -4964.89520399 -176590.88208536]
- [  -6265.28441518 -222842.99183237]
- [  -6768.1874191  -240730.1941634 ]
- [  -7157.01778976 -254560.07280431]]</t>
+          <t>[[-3367.723645256797, -119782.84831816258], [-6643.586972044864, -236298.41827484334], [-6778.466045582499, -241095.78329308282], [-7932.615036411789, -282146.4359200515], [-8645.375152476516, -307497.8144365351], [-9226.494522339823, -328167.008428483]]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -4397,7 +4199,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>post.constr_stress</t>
+          <t>post.hoop_stress_euro</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4405,15 +4207,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[[0.59458827 0.40790309]
- [0.64278593 0.4406581 ]
- [0.68136722 0.46421767]
- [0.67768504 0.45066698]
- [0.32058634 0.19260001]
- [0.09560274 0.0622088 ]]</t>
+          <t>[[-2189.020369416918, -77858.85140680568], [-4318.331531829162, -153593.97187864818], [-4406.002929628625, -156712.25914050383], [-5156.199773667663, -183395.18334803346], [-5619.4938491097355, -199873.57938374783], [-5997.221439520885, -213308.55547851394]]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -4421,7 +4222,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>post.constr_shell_buckling</t>
+          <t>post.constr_stress</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4432,12 +4233,7 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[[1.         0.54177077]
- [0.94914661 0.50722045]
- [0.88444985 0.46006876]
- [1.00000002 0.50827209]
- [0.31611109 0.14606247]
- [0.08306816 0.04940307]]</t>
+          <t>[[0.6392600477759149, 0.4758781332245894], [0.7067739286830983, 0.5233099913265465], [0.7798384455958256, 0.5731866821510762], [0.7648164154294166, 0.5581230565789379], [0.4112932989215037, 0.29572032169411694], [0.16248109586914233, 0.1257173590988928]]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -4445,7 +4241,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>post.constr_global_buckling</t>
+          <t>post.constr_shell_buckling</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4456,12 +4252,7 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[[0.75122279 0.5980166 ]
- [0.82087047 0.65517009]
- [0.90568913 0.728746  ]
- [1.00000001 0.81554775]
- [0.67031769 0.56546659]
- [0.42259744 0.39064451]]</t>
+          <t>[[0.9999999992387252, 0.6127026030607559], [0.9936415592964185, 0.5965946885886206], [1.0000000003064973, 0.5846262791829486], [0.9999999994556602, 0.578774402412417], [0.35250746801448984, 0.20074500836119868], [0.0883240395697717, 0.057921229668756874]]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -4469,7 +4260,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tower.f1</t>
+          <t>post.constr_global_buckling</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4477,14 +4268,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[0.24330369]</t>
+          <t>[[0.6676373636536678, 0.5344439675608726], [0.7459525023824234, 0.597933029866207], [0.8522983985793379, 0.6883010601544268], [0.9016440516063583, 0.7392721338433433], [0.5985162661479916, 0.5078660532458684], [0.3751708082705626, 0.34798570916884675]]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -4492,7 +4279,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tower.f2</t>
+          <t>tower.f1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4505,17 +4292,15 @@
           <t>Hz</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>[0.25992578]</t>
-        </is>
+      <c r="D175" t="n">
+        <v>0.247261605803669</v>
       </c>
       <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tower.structural_frequencies</t>
+          <t>tower.f2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4528,17 +4313,15 @@
           <t>Hz</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>[0.24330369 0.25992578 0.98828555 1.18399879 1.87534848 4.06245223]</t>
-        </is>
+      <c r="D176" t="n">
+        <v>0.2638657715901928</v>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tower.fore_aft_modes</t>
+          <t>tower.structural_frequencies</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4546,15 +4329,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[[ 8.77747213e-01 -1.08868792e+00  3.39484742e+00 -2.90217994e+00
-   7.18273228e-01]
- [ 2.79124365e+02 -3.68958465e+02  8.67572967e+02 -1.37515254e+03
-   5.98413671e+02]
- [-8.56133985e+01 -6.36366353e+00  3.17801473e+02 -2.32560531e+02
-   7.73611934e+00]]</t>
+          <t>[0.247261605803669, 0.26386577159019275, 1.0176288283152086, 1.214755241685765, 1.8985972124967792, 3.984103827806316]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -4562,7 +4344,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tower.side_side_modes</t>
+          <t>tower.fore_aft_modes</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4573,9 +4355,7 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[[  0.82627594  -1.00669471   3.1694976   -2.5917715    0.60269266]
- [  8.59567806 -12.84207799  34.64818602 -47.39054879  17.9887627 ]
- [-72.10732827  15.65507741 161.82372632 -63.97685487 -40.39462058]]</t>
+          <t>[[0.8522774567646689, -1.2352609200390594, 4.072301975589006, -3.7224810331573854, 1.0331625208428261], [-1062.7751837897615, 1268.4588307834526, -3188.7976183216315, 5445.699814755549, -2462.4366589514675], [-74.57110189180827, -45.803969479188815, 399.1508722593536, -320.16202343318065, 42.386222544824456]]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -4583,7 +4363,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tower.torsion_modes</t>
+          <t>tower.side_side_modes</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4594,9 +4374,7 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[[  8.39213201 -35.83665199  71.49626402 -64.84900151  21.79725748]
- [  0.           0.           0.           0.           0.        ]
- [  0.           0.           0.           0.           0.        ]]</t>
+          <t>[[0.8041497480878421, -1.159741657486074, 3.849254707540387, -3.405624546839774, 0.9119617486975574], [8.797074140034368, -12.896536507326113, 37.41343536949621, -53.085891418182186, 20.77191841597754], [-60.431379477135614, -11.628869429812136, 200.75838688818178, -107.10716721153644, -20.590970769697826]]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -4604,7 +4382,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>tower.fore_aft_freqs</t>
+          <t>tower.torsion_modes</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4612,14 +4390,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[0.25992578 1.87534848 4.47514264]</t>
+          <t>[[8.377751889712904, -35.037079823663845, 69.35092605481553, -62.83503564756766, 21.143437526703007], [0.0, 0.0, 0.0, 0.0, 0.0], [0.0, 0.0, 0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -4627,7 +4401,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>tower.side_side_freqs</t>
+          <t>tower.fore_aft_freqs</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4642,7 +4416,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[0.24330369 0.98828555 4.06245223]</t>
+          <t>[0.26386577159019275, 1.8985972124967792, 4.450442729887433]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -4650,7 +4424,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>tower.torsion_freqs</t>
+          <t>tower.side_side_freqs</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4665,7 +4439,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[6.6642043 0.        0.       ]</t>
+          <t>[0.247261605803669, 1.0176288283152086, 3.984103827806316]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -4673,7 +4447,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>tower.tower_deflection</t>
+          <t>tower.torsion_freqs</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4683,18 +4457,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[[0.         0.        ]
- [0.03070729 0.0220381 ]
- [0.12766844 0.09153326]
- [0.31096921 0.22265118]
- [0.60376535 0.43140997]
- [0.99291414 0.70761116]
- [1.43100315 1.01656751]]</t>
+          <t>[6.816141846486968, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -4702,7 +4470,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>tower.top_deflection</t>
+          <t>tower.tower_deflection</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4717,7 +4485,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[1.43100315 1.01656751]</t>
+          <t>[[0.0, 0.0], [0.02798845433210177, 0.020082604451003135], [0.11789078867041607, 0.08450318377494184], [0.29270571389447037, 0.20951235600612672], [0.5750110343655659, 0.4107260761692592], [0.9492959790374488, 0.6763131716856674], [1.3691450439484545, 0.9723998787991522]]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -4725,7 +4493,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>tower.tower_Fz</t>
+          <t>tower.top_deflection</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4735,17 +4503,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[[-4349646.81775228 -4872450.88627529]
- [-3955339.11065362 -4375164.32950331]
- [-3623649.11824756 -3938781.12201792]
- [-3381589.68356992 -3590328.5189508 ]
- [-3145064.16518961 -3237661.89709768]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[1.3691450439484545, 0.9723998787991522]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -4753,7 +4516,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>tower.tower_Vx</t>
+          <t>tower.tower_Fz</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4768,12 +4531,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[[1285223.92883864  930568.12549209]
- [1286054.13431463  931381.50956449]
- [1286827.30616763  932170.86795165]
- [1287171.46669971  932687.2888348 ]
- [1287893.29133193  933534.35080664]
- [1288201.35371041  933952.44178088]]</t>
+          <t>[[-4544592.622056397, -5059650.423935822], [-4105162.3238747856, -4516681.208264228], [-3742576.0671883076, -4051519.9310538517], [-3462389.8984045135, -3668148.7953211386], [-3186224.1643253956, -3278033.9326571384], [-2914124.844005121, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -4781,7 +4539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>tower.tower_Vy</t>
+          <t>tower.tower_Vx</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4796,12 +4554,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>[[ -18.2090241     8.34144263]
- [ -56.07168431   30.14563474]
- [-102.44697284   57.83271087]
- [-142.90930477   87.57210187]
- [-225.75952273  143.40405172]
- [-308.91537417  202.12683454]]</t>
+          <t>[[1285238.4043869115, 930576.6322370842], [1286097.8934733793, 931397.019623898], [1286916.2528408542, 932204.6731474921], [1287453.2592315823, 932837.2813826948], [1288280.5799453706, 933744.9353920519], [1288647.8186224997, 934202.6490297467]]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -4809,7 +4562,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>tower.tower_Mxx</t>
+          <t>tower.tower_Vy</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4819,17 +4572,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[[ 4297041.58485836 -1834651.88849187]
- [ 4278995.50136644 -1826025.02311278]
- [ 4243354.70033699 -1809201.36194055]
- [ 4180906.90705807 -1780251.68693602]
- [ 4086669.56457052 -1737601.6932439 ]
- [ 3963842.64578302 -1683740.94855524]]</t>
+          <t>[[-18.765764536336064, 8.53598613559734], [-58.02487879083492, 30.58131721999962], [-107.4146036352031, 59.15196234197356], [-160.36497919354588, 93.35996334557422], [-253.8755525201559, 152.6752626481466], [-346.8634190177545, 214.37659653648734]]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -4837,7 +4585,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>tower.tower_Myy</t>
+          <t>tower.tower_Mxx</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4852,12 +4600,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[[96402464.36660439 69106267.72841041]
- [77223950.80432796 55187110.18180166]
- [57742653.41236804 41032950.91426268]
- [37926035.15853652 26630228.20721585]
- [17855596.37986553 12058094.60763581]
- [-2274928.61633226 -2522316.0967429 ]]</t>
+          <t>[[4290877.763432895, -1831495.2536678775], [4273372.652325834, -1823180.615096555], [4237898.836773356, -1806529.7130356994], [4175375.814008143, -1777668.6551501239], [4082441.520206839, -1735707.0848135897], [3963851.324185379, -1683742.331208717]]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -4865,7 +4608,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>tower.tower_Mzz</t>
+          <t>tower.tower_Myy</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4880,12 +4623,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[[-346836.89386053  147328.21230941]
- [-346839.64786186  147329.55234485]
- [-346844.42504904  147331.45091846]
- [-346860.67810759  147338.44418837]
- [-346857.21350947  147336.03458721]
- [-346853.70101696  147333.46255849]]</t>
+          <t>[[96317618.26315734, 69030462.77466904], [77152307.69559985, 55123988.63890882], [57678444.10838093, 40978912.747313626], [37866284.06151751, 26583206.922303095], [17815762.835481524, 12028457.115821362], [-2274916.13560766, -2522314.562396005]]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -4893,7 +4631,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>tower.turbine_F</t>
+          <t>tower.tower_Mzz</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4903,14 +4641,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[[ 1.28474420e+06  9.30198601e+05]
- [ 1.04773790e-09  1.68802217e-09]
- [-4.80540298e+06 -5.37692967e+06]]</t>
+          <t>[[-346836.7097078701, 147327.95330848012], [-346839.7972184067, 147329.45402743277], [-346845.3753805976, 147331.7378701903], [-346856.97858079086, 147336.59471315128], [-346852.4262340079, 147333.80635760282], [-346847.8133335625, 147330.8703587166]]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -4918,7 +4654,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>tower.turbine_M</t>
+          <t>tower.turbine_F</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4928,14 +4664,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[[ 4.30260768e+06 -1.83731232e+06]
- [ 1.15306102e+08  8.28048017e+07]
- [-3.46781682e+05  1.47301970e+05]]</t>
+          <t>[[1284744.1962051503, 930198.6006328166], [7.334165275096893e-09, 4.0745362639427185e-10], [-5059645.232468988, -5624299.737090186]]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -4943,7 +4677,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>turbine_mass</t>
+          <t>tower.turbine_M</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4953,12 +4687,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[477071.27476739]</t>
+          <t>[[4296218.65848998, -1834030.6108441453], [115215277.31412035, 82723431.44542007], [-346781.68192839005, 147301.97023764014]]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -4966,7 +4700,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>turbine_center_of_mass</t>
+          <t>turbine_mass</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4976,20 +4710,18 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>[-0.67765783  0.         67.62467733]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>503013.6618441729</v>
       </c>
       <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>turbine_I_base</t>
+          <t>turbine_center_of_mass</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4999,13 +4731,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[2.69242119e+09 2.59952592e+09 1.99907339e+07 0.00000000e+00
- 5.03710467e+05 0.00000000e+00]</t>
+          <t>[-0.6427083630355379, 0.0, 66.23927077311454]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5013,7 +4744,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>constr_d_to_t</t>
+          <t>turbine_I_base</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5021,10 +4752,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>[311.69875231 281.32545841]</t>
+          <t>[2754259058.4478197, 2661363783.4478197, 20159317.687618833, 0.0, 503710.467, 0.0]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5032,7 +4767,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>constr_taper</t>
+          <t>constr_d_to_t</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5043,7 +4778,7 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[0.61414324 0.92908536]</t>
+          <t>[282.04679449246345, 233.74875409192987]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5051,7 +4786,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>slope</t>
+          <t>constr_taper</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5062,7 +4797,7 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[0.61414324 0.92908536]</t>
+          <t>[0.5838450756361844, 0.9545046917589489]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5070,7 +4805,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>thickness_slope</t>
+          <t>slope</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5081,7 +4816,7 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[0.81321444]</t>
+          <t>[0.5838450756361844, 0.9545046917589489]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -5089,7 +4824,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>member.ca_usr_grid_full</t>
+          <t>thickness_slope</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5098,17 +4833,15 @@
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+      <c r="D200" t="n">
+        <v>0.8693476885344393</v>
       </c>
       <c r="E200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>member.cd_usr_grid_full</t>
+          <t>member.ca_usr_grid_full</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5119,7 +4852,7 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -5127,7 +4860,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>member.nu_full</t>
+          <t>member.cd_usr_grid_full</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5138,7 +4871,7 @@
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[0.29950495 0.29950495 0.29950495 0.29950495 0.29950495 0.29950495]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -5146,7 +4879,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>member.nodes_r</t>
+          <t>member.nu_full</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5154,15 +4887,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[3.39121773 2.95504298 2.51886822 2.08269346 2.03346231 1.98423115
- 1.935     ]</t>
+          <t>[0.29950495049504955, 0.29950495049504955, 0.29950495049504955, 0.29950495049504955, 0.29950495049504955, 0.29950495049504955]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -5170,7 +4898,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>member.center_of_buoyancy</t>
+          <t>member.nodes_r</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5185,7 +4913,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[3.4722043779833762, 2.9905460612182493, 2.508887744453122, 2.027229427687995, 1.99648628512533, 1.965743142562665, 1.935]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -5193,7 +4921,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>member.displacement</t>
+          <t>member.center_of_buoyancy</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5203,12 +4931,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -5216,7 +4944,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>member.buoyancy_force</t>
+          <t>member.displacement</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5226,20 +4954,18 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m**3</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
       </c>
       <c r="E206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>member.idx_cb</t>
+          <t>member.buoyancy_force</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5247,18 +4973,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
       </c>
       <c r="E207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>member.Awater</t>
+          <t>member.idx_cb</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5266,22 +4994,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="n">
+        <v>0</v>
       </c>
       <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>member.Iwaterx</t>
+          <t>member.Awater</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5291,20 +5013,18 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>m**4</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m**2</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
       </c>
       <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>member.Iwatery</t>
+          <t>member.Iwaterx</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5317,17 +5037,15 @@
           <t>m**4</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D210" t="n">
+        <v>0</v>
       </c>
       <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>member.added_mass</t>
+          <t>member.Iwatery</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5337,20 +5055,18 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>m**4</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
       </c>
       <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>member.waterline_centroid</t>
+          <t>member.added_mass</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5360,12 +5076,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -5373,7 +5089,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>member.z_dim</t>
+          <t>member.waterline_centroid</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5388,7 +5104,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[ 0.  14.6 29.2 43.8 58.4 73.  87.6]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -5396,7 +5112,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>member.d_eff</t>
+          <t>member.z_dim</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5411,8 +5127,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>[6.78243547 5.91008595 5.03773644 4.16538692 4.06692462 3.96846231
- 3.87      ]</t>
+          <t>[0.0, 14.599999999999998, 29.199999999999996, 43.8, 58.39999999999999, 72.99999999999999, 87.6]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -5420,7 +5135,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>tower_section_height</t>
+          <t>member.d_eff</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5435,7 +5150,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[43.8 43.8]</t>
+          <t>[6.9444087559667524, 5.981092122436499, 5.017775488906244, 4.05445885537599, 3.99297257025066, 3.93148628512533, 3.87]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -5443,7 +5158,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>member.sigma_ult</t>
+          <t>tower_section_height</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5453,12 +5168,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>[6.e+08 6.e+08]</t>
+          <t>[43.8, 43.8]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -5466,7 +5181,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>member.wohler_exp</t>
+          <t>member.sigma_ult</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5474,10 +5189,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>[10. 10.]</t>
+          <t>[600000000.0, 600000000.0]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -5485,7 +5204,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>member.wohler_A</t>
+          <t>member.wohler_exp</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5496,7 +5215,7 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>[10. 10.]</t>
+          <t>[10.0, 10.0]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -5504,7 +5223,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>member.ballast_density</t>
+          <t>member.wohler_A</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5512,14 +5231,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[10.0, 10.0]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -5527,7 +5242,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>member.ballast_unit_cost</t>
+          <t>member.ballast_density</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5537,7 +5252,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5550,7 +5265,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>z_param</t>
+          <t>member.ballast_unit_cost</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5560,12 +5275,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>[ 0.  43.8 87.6]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -5573,7 +5288,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>member.sec_loc</t>
+          <t>z_param</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5581,22 +5296,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>[0. 1.]</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>normalized sectional location</t>
-        </is>
-      </c>
+          <t>[0.0, 43.8, 87.6]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>member.str_tw</t>
+          <t>member.sec_loc</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5604,26 +5319,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>structural twist of section</t>
+          <t>normalized sectional location</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>member.tw_iner</t>
+          <t>member.str_tw</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5638,19 +5349,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>inertial twist of section</t>
+          <t>structural twist of section</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>member.mass_den</t>
+          <t>member.tw_iner</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5660,24 +5371,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>kg/m</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>[2737.89918715 1633.61850161]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>sectional mass per unit length</t>
+          <t>inertial twist of section</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>member.foreaft_iner</t>
+          <t>member.mass_den</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5687,24 +5398,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>kg*m</t>
+          <t>kg/m</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>[10189.11234239  3272.85519937]</t>
+          <t>[3052.986148063437, 1910.8234830821]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>sectional fore-aft intertia per unit length about the Y_G inertia axis</t>
+          <t>sectional mass per unit length</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>member.sideside_iner</t>
+          <t>member.foreaft_iner</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5719,19 +5430,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[10189.11234239  3272.85519937]</t>
+          <t>[11460.174726023082, 3717.8679321010723]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>sectional side-side intertia per unit length about the Y_G inertia axis</t>
+          <t>sectional fore-aft intertia per unit length about the Y_G inertia axis</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>member.foreaft_stff</t>
+          <t>member.sideside_iner</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5741,24 +5452,24 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>N*m**2</t>
+          <t>kg*m</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>[2.35262627e+11 7.55689491e+10]</t>
+          <t>[11460.174726023082, 3717.8679321010723]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>sectional fore-aft bending stiffness per unit length about the Y_E elastic axis</t>
+          <t>sectional side-side intertia per unit length about the Y_G inertia axis</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>member.sideside_stff</t>
+          <t>member.foreaft_stff</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5773,19 +5484,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[2.35262627e+11 7.55689491e+10]</t>
+          <t>[264610961238.57584, 85844119377.81476]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>sectional side-side bending stiffness per unit length about the Y_E elastic axis</t>
+          <t>sectional fore-aft bending stiffness per unit length about the Y_E elastic axis</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>member.tor_stff</t>
+          <t>member.sideside_stff</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5800,19 +5511,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[1.81040193e+11 5.81521056e+10]</t>
+          <t>[264610961238.57584, 85844119377.81476]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>sectional torsional stiffness</t>
+          <t>sectional side-side bending stiffness per unit length about the Y_E elastic axis</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>member.axial_stff</t>
+          <t>member.tor_stff</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5822,24 +5533,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N*m**2</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[6.32170236e+10 3.77196136e+10]</t>
+          <t>[203624434934.06598, 66059093768.83269]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>sectional axial stiffness</t>
+          <t>sectional torsional stiffness</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>member.cg_offst</t>
+          <t>member.axial_stff</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5849,24 +5560,24 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[70492258503.93863, 44120168383.423965]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>offset from the sectional center of mass</t>
+          <t>sectional axial stiffness</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>member.sc_offst</t>
+          <t>member.cg_offst</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5881,19 +5592,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>offset from the sectional shear center</t>
+          <t>offset from the sectional center of mass</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>member.tc_offst</t>
+          <t>member.sc_offst</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5908,19 +5619,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>offset from the sectional tension center</t>
+          <t>offset from the sectional shear center</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>member.axial_load2stress</t>
+          <t>member.tc_offst</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5930,21 +5641,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>[[0.         0.         3.32189003 2.44305984 2.44305984 0.        ]
- [0.         0.         5.56739532 5.58242266 5.58242266 0.        ]]</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>[0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>offset from the sectional tension center</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>member.shear_load2stress</t>
+          <t>member.axial_load2stress</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5959,8 +5673,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>[[5.46311879 5.46311879 0.         0.         0.         1.22152992]
- [9.15460684 9.15460684 0.         0.         0.         2.79121133]]</t>
+          <t>[[0.6263816023667158, 0.6263816023667158, 2.979050529190615, 2.1822246020824054, 2.1822246020824054, 0.0], [0.6263816023667158, 0.6263816023667158, 4.759727981430311, 4.846390095472956, 4.846390095472956, 0.0]]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -5968,7 +5681,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>member.labor_hours</t>
+          <t>member.shear_load2stress</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5978,12 +5691,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[185.68907442]</t>
+          <t>[[4.898547097345639, 4.898547097345639, 0.0, 0.0, 0.0, 1.0911123010412027], [7.823977143442525, 7.823977143442525, 0.0, 0.0, 0.0, 2.423195047736478]]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -5991,7 +5704,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>tower_cost</t>
+          <t>member.labor_hours</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6001,20 +5714,18 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>[963249.15343406]</t>
-        </is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>200.013479588192</v>
       </c>
       <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>member.section_D</t>
+          <t>tower_cost</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6024,20 +5735,18 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>[6.34626071 5.4739112  4.60156168 4.11615577 4.01769346 3.91923115]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1067893.996631479</v>
       </c>
       <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>member.section_t</t>
+          <t>member.section_D</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6052,7 +5761,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>[0.01879085 0.01879085 0.01879085 0.01528099 0.01528099 0.01528099]</t>
+          <t>[6.462750439201626, 5.499433805671371, 4.536117172141116, 4.023715712813325, 3.962229427687995, 3.900743142562665]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6060,7 +5769,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>member.section_sigma_y</t>
+          <t>member.section_t</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6070,12 +5779,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>[4.5e+08 4.5e+08 4.5e+08 4.5e+08 4.5e+08 4.5e+08]</t>
+          <t>[0.019498302810239246, 0.019498302810239246, 0.019498302810239246, 0.016950804478426052, 0.016950804478426052, 0.016950804478426052]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -6083,7 +5792,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>height_constraint</t>
+          <t>member.section_sigma_y</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6093,12 +5802,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[450000000.0, 450000000.0, 450000000.0, 450000000.0, 450000000.0, 450000000.0]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -6106,7 +5815,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>transition_piece_height</t>
+          <t>height_constraint</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6119,35 +5828,52 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D243" t="n">
+        <v>0</v>
       </c>
       <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t>transition_piece_height</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>z_start</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
